--- a/Tables/taxa_summary_Figure2.xlsx
+++ b/Tables/taxa_summary_Figure2.xlsx
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>1121</v>
+        <v>1110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -411,21 +411,21 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.4668887963348605</v>
+        <v>0.4644351464435146</v>
       </c>
       <c r="E2">
-        <v>0.4668887963348605</v>
+        <v>0.4644351464435146</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.09337775926697209</v>
+        <v>0.09288702928870293</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Mussels
-(n=1121)</t>
+(n=1110)</t>
         </is>
       </c>
     </row>
@@ -444,16 +444,16 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.2957101207830071</v>
+        <v>0.297071129707113</v>
       </c>
       <c r="E3">
-        <v>0.7625989171178675</v>
+        <v>0.7615062761506276</v>
       </c>
       <c r="F3">
-        <v>0.4668887963348605</v>
+        <v>0.4644351464435146</v>
       </c>
       <c r="G3">
-        <v>0.2458975426905456</v>
+        <v>0.2451882845188285</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.1278633902540608</v>
+        <v>0.1284518828451883</v>
       </c>
       <c r="E4">
-        <v>0.8904623073719283</v>
+        <v>0.8899581589958159</v>
       </c>
       <c r="F4">
-        <v>0.7625989171178675</v>
+        <v>0.7615062761506276</v>
       </c>
       <c r="G4">
-        <v>0.3306122448979592</v>
+        <v>0.3302928870292887</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.06080799666805498</v>
+        <v>0.06108786610878661</v>
       </c>
       <c r="E5">
-        <v>0.9512703040399832</v>
+        <v>0.9510460251046025</v>
       </c>
       <c r="F5">
-        <v>0.8904623073719283</v>
+        <v>0.8899581589958159</v>
       </c>
       <c r="G5">
-        <v>0.3683465222823823</v>
+        <v>0.3682008368200836</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.01374427321949188</v>
+        <v>0.01380753138075314</v>
       </c>
       <c r="E6">
-        <v>0.9650145772594751</v>
+        <v>0.9648535564853556</v>
       </c>
       <c r="F6">
-        <v>0.9512703040399832</v>
+        <v>0.9510460251046025</v>
       </c>
       <c r="G6">
-        <v>0.3832569762598917</v>
+        <v>0.3831799163179916</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0129112869637651</v>
+        <v>0.01297071129707113</v>
       </c>
       <c r="E7">
-        <v>0.9779258642232402</v>
+        <v>0.9778242677824268</v>
       </c>
       <c r="F7">
-        <v>0.9650145772594751</v>
+        <v>0.9648535564853556</v>
       </c>
       <c r="G7">
-        <v>0.3885880882965431</v>
+        <v>0.3885355648535565</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -609,16 +609,16 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.01166180758017493</v>
+        <v>0.01171548117154812</v>
       </c>
       <c r="E8">
-        <v>0.9895876718034151</v>
+        <v>0.9895397489539749</v>
       </c>
       <c r="F8">
-        <v>0.9779258642232402</v>
+        <v>0.9778242677824268</v>
       </c>
       <c r="G8">
-        <v>0.3935027072053311</v>
+        <v>0.3934728033472804</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.007496876301541024</v>
+        <v>0.007531380753138075</v>
       </c>
       <c r="E9">
-        <v>0.9970845481049562</v>
+        <v>0.997071129707113</v>
       </c>
       <c r="F9">
-        <v>0.9895876718034151</v>
+        <v>0.9895397489539749</v>
       </c>
       <c r="G9">
-        <v>0.3973344439816743</v>
+        <v>0.3973221757322176</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.002915451895043732</v>
+        <v>0.002928870292887029</v>
       </c>
       <c r="E10">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0.9970845481049562</v>
+        <v>0.997071129707113</v>
       </c>
       <c r="G10">
-        <v>0.3994169096209912</v>
+        <v>0.3994142259414226</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
